--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -606,10 +606,10 @@
         <v>0.248152</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -3057,10 +3057,10 @@
         <v>0.946917</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -4261,10 +4261,10 @@
         <v>0.959709</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -4780,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.666667</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.666667</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>0.294007</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>0.099581</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0.333333</v>
+        <v>0.09859900000000001</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.333333</v>
+        <v>0.306177</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0.333333</v>
+        <v>0.106907</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.333333</v>
+        <v>0.104998</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.333333</v>
+        <v>0.307636</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>0.186753</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>0.087199</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>0.102444</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>0.093296</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>0.195927</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>0.195312</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6024,10 +6024,10 @@
         <v>0.667476</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.666667</v>
+        <v>0.2999</v>
       </c>
       <c r="J130" t="n">
         <v>1</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0.333333</v>
+        <v>0.102033</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>0.091489</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>0.091082</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>0.095233</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>0.268443</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0.333333</v>
+        <v>0.099426</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>0.098368</v>
       </c>
       <c r="J144" t="n">
         <v>1</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0.333333</v>
+        <v>0.10665</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0.333333</v>
+        <v>0.210139</v>
       </c>
       <c r="J146" t="n">
         <v>1</v>
@@ -6801,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>0.091879</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -6887,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>0.08960700000000001</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0.333333</v>
+        <v>0.195977</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
@@ -6973,7 +6973,7 @@
         <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.666667</v>
+        <v>0.513177</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>0.097969</v>
       </c>
       <c r="J154" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>0.08259</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>0.193226</v>
       </c>
       <c r="J162" t="n">
         <v>1</v>
@@ -7446,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>0.196566</v>
       </c>
       <c r="J163" t="n">
         <v>1</v>
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0.333333</v>
+        <v>0.20016</v>
       </c>
       <c r="J164" t="n">
         <v>1</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>0.094074</v>
       </c>
       <c r="J166" t="n">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J168" t="n">
         <v>1</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>0.333333</v>
+        <v>0.199566</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -7790,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>0.096114</v>
       </c>
       <c r="J171" t="n">
         <v>1</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0.333333</v>
+        <v>0.191188</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>0.100604</v>
       </c>
       <c r="J174" t="n">
         <v>1</v>
@@ -8005,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>0.333333</v>
+        <v>0.108723</v>
       </c>
       <c r="J176" t="n">
         <v>1</v>
@@ -8220,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0.333333</v>
+        <v>0.199178</v>
       </c>
       <c r="J181" t="n">
         <v>1</v>
@@ -8306,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>0.094875</v>
       </c>
       <c r="J183" t="n">
         <v>1</v>
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>0.189752</v>
       </c>
       <c r="J184" t="n">
         <v>1</v>
@@ -8392,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>0.288057</v>
       </c>
       <c r="J185" t="n">
         <v>1</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>0.09660100000000001</v>
       </c>
       <c r="J186" t="n">
         <v>1</v>
@@ -8478,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>0.189054</v>
       </c>
       <c r="J187" t="n">
         <v>1</v>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>0.097054</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>0.096591</v>
       </c>
       <c r="J192" t="n">
         <v>1</v>
@@ -8736,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>0.290242</v>
       </c>
       <c r="J193" t="n">
         <v>1</v>
@@ -8779,7 +8779,7 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>0.192681</v>
       </c>
       <c r="J194" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>0.09568400000000001</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>0.103199</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>0.191565</v>
       </c>
       <c r="J198" t="n">
         <v>1</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0.333333</v>
+        <v>0.301041</v>
       </c>
       <c r="J199" t="n">
         <v>1</v>
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>0.189663</v>
       </c>
       <c r="J200" t="n">
         <v>1</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>0.333333</v>
+        <v>0.202536</v>
       </c>
       <c r="J201" t="n">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -10155,7 +10155,7 @@
         <v>0</v>
       </c>
       <c r="I226" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J226" t="n">
         <v>1</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -10499,7 +10499,7 @@
         <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -11058,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -11485,10 +11485,10 @@
         <v>0.810847</v>
       </c>
       <c r="H257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J257" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -11703,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J268" t="n">
         <v>1</v>
@@ -12732,10 +12732,10 @@
         <v>0.308126</v>
       </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -13982,7 +13982,7 @@
         <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>0.395912</v>
+        <v>0.333333</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>0.391377</v>
+        <v>0.333333</v>
       </c>
       <c r="J316" t="n">
         <v>1</v>
@@ -14068,7 +14068,7 @@
         <v>0</v>
       </c>
       <c r="I317" t="n">
-        <v>0.194818</v>
+        <v>0</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -14154,7 +14154,7 @@
         <v>0</v>
       </c>
       <c r="I319" t="n">
-        <v>0.16317</v>
+        <v>0</v>
       </c>
       <c r="J319" t="n">
         <v>0</v>
@@ -14197,7 +14197,7 @@
         <v>0</v>
       </c>
       <c r="I320" t="n">
-        <v>0.205525</v>
+        <v>0.333333</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -14541,7 +14541,7 @@
         <v>0</v>
       </c>
       <c r="I328" t="n">
-        <v>0.205416</v>
+        <v>0.333333</v>
       </c>
       <c r="J328" t="n">
         <v>1</v>
@@ -14670,7 +14670,7 @@
         <v>0</v>
       </c>
       <c r="I331" t="n">
-        <v>0.259262</v>
+        <v>0.333333</v>
       </c>
       <c r="J331" t="n">
         <v>1</v>
@@ -14713,7 +14713,7 @@
         <v>0</v>
       </c>
       <c r="I332" t="n">
-        <v>0.196975</v>
+        <v>0</v>
       </c>
       <c r="J332" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
         <v>1</v>
       </c>
       <c r="I333" t="n">
-        <v>0.662006</v>
+        <v>1</v>
       </c>
       <c r="J333" t="n">
         <v>1</v>
@@ -15143,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>0.152978</v>
+        <v>0</v>
       </c>
       <c r="J342" t="n">
         <v>0</v>
@@ -15272,7 +15272,7 @@
         <v>0</v>
       </c>
       <c r="I345" t="n">
-        <v>0.188208</v>
+        <v>0</v>
       </c>
       <c r="J345" t="n">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
-        <v>0.372206</v>
+        <v>0</v>
       </c>
       <c r="J346" t="n">
         <v>1</v>
@@ -15358,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>0.194146</v>
+        <v>0</v>
       </c>
       <c r="J347" t="n">
         <v>0</v>
@@ -15401,7 +15401,7 @@
         <v>0</v>
       </c>
       <c r="I348" t="n">
-        <v>0.198469</v>
+        <v>0</v>
       </c>
       <c r="J348" t="n">
         <v>0</v>
@@ -15530,7 +15530,7 @@
         <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>0.21051</v>
+        <v>0.333333</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
@@ -15573,7 +15573,7 @@
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>0.180627</v>
+        <v>0</v>
       </c>
       <c r="J352" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>0.18156</v>
+        <v>0</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -15831,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>0.206981</v>
+        <v>0.333333</v>
       </c>
       <c r="J358" t="n">
         <v>1</v>
@@ -15917,7 +15917,7 @@
         <v>0</v>
       </c>
       <c r="I360" t="n">
-        <v>0.178674</v>
+        <v>0</v>
       </c>
       <c r="J360" t="n">
         <v>0</v>
@@ -16003,7 +16003,7 @@
         <v>0</v>
       </c>
       <c r="I362" t="n">
-        <v>0.400781</v>
+        <v>0.333333</v>
       </c>
       <c r="J362" t="n">
         <v>0</v>
@@ -16086,10 +16086,10 @@
         <v>0.428729</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5782659999999999</v>
+        <v>0.333333</v>
       </c>
       <c r="J364" t="n">
         <v>0</v>
@@ -16132,7 +16132,7 @@
         <v>0</v>
       </c>
       <c r="I365" t="n">
-        <v>0.180157</v>
+        <v>0</v>
       </c>
       <c r="J365" t="n">
         <v>0</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="I367" t="n">
-        <v>0.197622</v>
+        <v>0</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>0</v>
       </c>
       <c r="I368" t="n">
-        <v>0.244895</v>
+        <v>0.333333</v>
       </c>
       <c r="J368" t="n">
         <v>0</v>
@@ -16476,7 +16476,7 @@
         <v>0</v>
       </c>
       <c r="I373" t="n">
-        <v>0.199474</v>
+        <v>0.333333</v>
       </c>
       <c r="J373" t="n">
         <v>0</v>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>0.197126</v>
+        <v>0</v>
       </c>
       <c r="J375" t="n">
         <v>0</v>
@@ -16691,7 +16691,7 @@
         <v>0</v>
       </c>
       <c r="I378" t="n">
-        <v>0.197613</v>
+        <v>0</v>
       </c>
       <c r="J378" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="I380" t="n">
-        <v>0.42936</v>
+        <v>0.333333</v>
       </c>
       <c r="J380" t="n">
         <v>1</v>
@@ -16863,7 +16863,7 @@
         <v>0</v>
       </c>
       <c r="I382" t="n">
-        <v>0.25676</v>
+        <v>0.333333</v>
       </c>
       <c r="J382" t="n">
         <v>1</v>
@@ -17078,7 +17078,7 @@
         <v>0</v>
       </c>
       <c r="I387" t="n">
-        <v>0.183501</v>
+        <v>0</v>
       </c>
       <c r="J387" t="n">
         <v>0</v>
@@ -17207,7 +17207,7 @@
         <v>0</v>
       </c>
       <c r="I390" t="n">
-        <v>0.191143</v>
+        <v>0</v>
       </c>
       <c r="J390" t="n">
         <v>0</v>
@@ -17293,7 +17293,7 @@
         <v>0</v>
       </c>
       <c r="I392" t="n">
-        <v>0.205212</v>
+        <v>0.333333</v>
       </c>
       <c r="J392" t="n">
         <v>0</v>
@@ -17333,10 +17333,10 @@
         <v>0.412623</v>
       </c>
       <c r="H393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I393" t="n">
-        <v>0.409637</v>
+        <v>0.666667</v>
       </c>
       <c r="J393" t="n">
         <v>0</v>
@@ -17422,7 +17422,7 @@
         <v>1</v>
       </c>
       <c r="I395" t="n">
-        <v>0.599709</v>
+        <v>0.666667</v>
       </c>
       <c r="J395" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>0</v>
       </c>
       <c r="I397" t="n">
-        <v>0.19022</v>
+        <v>0.333333</v>
       </c>
       <c r="J397" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
         <v>0</v>
       </c>
       <c r="I398" t="n">
-        <v>0.18487</v>
+        <v>0</v>
       </c>
       <c r="J398" t="n">
         <v>0</v>
@@ -17637,7 +17637,7 @@
         <v>0</v>
       </c>
       <c r="I400" t="n">
-        <v>0.188202</v>
+        <v>0</v>
       </c>
       <c r="J400" t="n">
         <v>0</v>
@@ -17723,7 +17723,7 @@
         <v>0</v>
       </c>
       <c r="I402" t="n">
-        <v>0.203002</v>
+        <v>0.333333</v>
       </c>
       <c r="J402" t="n">
         <v>0</v>
@@ -17766,7 +17766,7 @@
         <v>0</v>
       </c>
       <c r="I403" t="n">
-        <v>0.181517</v>
+        <v>0</v>
       </c>
       <c r="J403" t="n">
         <v>1</v>
@@ -17895,7 +17895,7 @@
         <v>0</v>
       </c>
       <c r="I406" t="n">
-        <v>0.202026</v>
+        <v>0.333333</v>
       </c>
       <c r="J406" t="n">
         <v>0</v>
@@ -17938,7 +17938,7 @@
         <v>0</v>
       </c>
       <c r="I407" t="n">
-        <v>0.389583</v>
+        <v>0.333333</v>
       </c>
       <c r="J407" t="n">
         <v>0</v>
@@ -17981,7 +17981,7 @@
         <v>0</v>
       </c>
       <c r="I408" t="n">
-        <v>0.184604</v>
+        <v>0.333333</v>
       </c>
       <c r="J408" t="n">
         <v>0</v>
@@ -18236,10 +18236,10 @@
         <v>0.869072</v>
       </c>
       <c r="H414" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I414" t="n">
-        <v>0.583645</v>
+        <v>0.333333</v>
       </c>
       <c r="J414" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.309124</v>
+        <v>0.218084</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.959694</v>
+        <v>0.972172</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.248152</v>
+        <v>0.108168</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>0.660318</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.723602</v>
+        <v>0.463475</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -686,10 +686,10 @@
         <v>0.000327</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.514202</v>
+        <v>0.429003</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5301360000000001</v>
+        <v>0.554947</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -772,10 +772,10 @@
         <v>1.8e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.694134</v>
+        <v>0.40215</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0.000833</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.628951</v>
+        <v>0.372984</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.667421</v>
+        <v>0.576693</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.168922</v>
+        <v>0.079219</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.964012</v>
+        <v>0.976527</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.47199</v>
+        <v>0.205971</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.289818</v>
+        <v>0.11517</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.292952</v>
+        <v>0.102917</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.333343</v>
+        <v>0.196499</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>5e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.53445</v>
+        <v>0.140721</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.115096</v>
+        <v>0.07283100000000001</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.27681</v>
+        <v>0.10806</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.212411</v>
+        <v>0.054645</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.200479</v>
+        <v>0.074008</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>0.993175</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.680484</v>
+        <v>0.420401</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.258703</v>
+        <v>0.086711</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.273264</v>
+        <v>0.069497</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.275078</v>
+        <v>0.110539</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.275171</v>
+        <v>0.130416</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.438359</v>
+        <v>0.354749</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.398942</v>
+        <v>0.264555</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.338043</v>
+        <v>0.120419</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.879358</v>
+        <v>0.6304110000000001</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.294949</v>
+        <v>0.103364</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.253828</v>
+        <v>0.119867</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.319504</v>
+        <v>0.138179</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.817123</v>
+        <v>0.872774</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.446091</v>
+        <v>0.327269</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4859</v>
+        <v>0.215905</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2019,10 +2019,10 @@
         <v>0.156881</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.544273</v>
+        <v>0.203418</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.512505</v>
+        <v>0.530437</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.129138</v>
+        <v>0.06544999999999999</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.484565</v>
+        <v>0.230322</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.384213</v>
+        <v>0.16279</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.222972</v>
+        <v>0.08183600000000001</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.280067</v>
+        <v>0.105154</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.253443</v>
+        <v>0.078045</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0.896954</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.526357</v>
+        <v>0.244373</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.418257</v>
+        <v>0.321825</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.392478</v>
+        <v>0.176847</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.461327</v>
+        <v>0.173712</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7037679999999999</v>
+        <v>0.635925</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.471208</v>
+        <v>0.15816</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         <v>0.085506</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.585807</v>
+        <v>0.291754</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.990601</v>
+        <v>0.997628</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.185175</v>
+        <v>0.088435</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.647491</v>
+        <v>0.5732350000000001</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.326069</v>
+        <v>0.135702</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.199268</v>
+        <v>0.059468</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.439168</v>
+        <v>0.158432</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.245854</v>
+        <v>0.054926</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.462061</v>
+        <v>0.269361</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3008,10 +3008,10 @@
         <v>0.000531</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.564775</v>
+        <v>0.324857</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.946917</v>
+        <v>0.980478</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.259669</v>
+        <v>0.138856</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.931768</v>
+        <v>0.894085</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.303758</v>
+        <v>0.207154</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>0.000341</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.51239</v>
+        <v>0.357348</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.302655</v>
+        <v>0.150492</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.353511</v>
+        <v>0.330426</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.286251</v>
+        <v>0.124266</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.382784</v>
+        <v>0.248897</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.151602</v>
+        <v>0.054173</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.455351</v>
+        <v>0.284822</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.299738</v>
+        <v>0.120638</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.250862</v>
+        <v>0.150438</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.388939</v>
+        <v>0.397118</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>0.030045</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.57097</v>
+        <v>0.400016</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.81223</v>
+        <v>0.658354</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.933705</v>
+        <v>0.958356</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.550214</v>
+        <v>0.635252</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -3825,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.519502</v>
+        <v>0.294391</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.138497</v>
+        <v>0.062438</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3911,10 +3911,10 @@
         <v>0.022414</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6182530000000001</v>
+        <v>0.441581</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -3954,10 +3954,10 @@
         <v>0.009516</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.632278</v>
+        <v>0.4943</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
@@ -3997,10 +3997,10 @@
         <v>0.043954</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.511769</v>
+        <v>0.33526</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.333409</v>
+        <v>0.120595</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.310814</v>
+        <v>0.102273</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4126,10 +4126,10 @@
         <v>4e-06</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.741865</v>
+        <v>0.460642</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.09492</v>
+        <v>0.038908</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.278286</v>
+        <v>0.25718</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.959709</v>
+        <v>0.967368</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.137164</v>
+        <v>0.048406</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.168619</v>
+        <v>0.070226</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.15004</v>
+        <v>0.047354</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.363011</v>
+        <v>0.193922</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0.815848</v>
+        <v>0.894231</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.745183</v>
+        <v>0.63654</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0.097967</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.652843</v>
+        <v>0.268905</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.261607</v>
+        <v>0.100465</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.326172</v>
+        <v>0.152177</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.997422</v>
+        <v>0.99977</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.245677</v>
+        <v>0.115486</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.954464</v>
+        <v>0.982199</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.9692730000000001</v>
+        <v>0.973059</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
         <v>0.000354</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.643411</v>
+        <v>0.384027</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.335871</v>
+        <v>0.126556</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.11599</v>
+        <v>0.052496</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.720819</v>
+        <v>0.699573</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.382666</v>
+        <v>0.346592</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.160087</v>
+        <v>0.037364</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.7917380000000001</v>
+        <v>0.828495</v>
       </c>
       <c r="H206" t="n">
         <v>1</v>
@@ -9329,10 +9329,10 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0.351077</v>
+        <v>0.54383</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.213429</v>
+        <v>0.140728</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.341835</v>
+        <v>0.167363</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.660693</v>
+        <v>0.784199</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.185563</v>
+        <v>0.070314</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.309134</v>
+        <v>0.181709</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.277468</v>
+        <v>0.163583</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.278079</v>
+        <v>0.127978</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.212171</v>
+        <v>0.113796</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.364969</v>
+        <v>0.184149</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.281907</v>
+        <v>0.115002</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.373162</v>
+        <v>0.462385</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.274761</v>
+        <v>0.168271</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.317961</v>
+        <v>0.197595</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.346514</v>
+        <v>0.225899</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>0.37464</v>
+        <v>0.307998</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.396465</v>
+        <v>0.322293</v>
       </c>
       <c r="H223" t="n">
         <v>1</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.191048</v>
+        <v>0.155407</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.421636</v>
+        <v>0.437031</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.350149</v>
+        <v>0.1994</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>0.530868</v>
+        <v>0.583931</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.260808</v>
+        <v>0.184659</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.234562</v>
+        <v>0.132877</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.186447</v>
+        <v>0.113538</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.639863</v>
+        <v>0.708719</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.231111</v>
+        <v>0.137468</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.518811</v>
+        <v>0.840659</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.470754</v>
+        <v>0.397335</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.824252</v>
+        <v>0.928001</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.182518</v>
+        <v>0.07885200000000001</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.229961</v>
+        <v>0.267928</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.216372</v>
+        <v>0.145369</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.193216</v>
+        <v>0.094634</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.198062</v>
+        <v>0.101463</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.103374</v>
+        <v>0.069281</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.157106</v>
+        <v>0.080957</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.45109</v>
+        <v>0.272471</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10920,10 +10920,10 @@
         <v>0.000416</v>
       </c>
       <c r="F244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.573016</v>
+        <v>0.475213</v>
       </c>
       <c r="H244" t="n">
         <v>1</v>
@@ -10966,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.552573</v>
+        <v>0.863856</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.551702</v>
+        <v>0.523802</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.868416</v>
+        <v>0.985998</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>0.3197</v>
+        <v>0.479133</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.736928</v>
+        <v>0.985976</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.22185</v>
+        <v>0.184613</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.311228</v>
+        <v>0.298319</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0.057296</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.495724</v>
+        <v>0.808456</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.181449</v>
+        <v>0.09288299999999999</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.305687</v>
+        <v>0.322053</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="G255" t="n">
-        <v>0.763207</v>
+        <v>0.850055</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.696264</v>
+        <v>0.8536550000000001</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.810847</v>
+        <v>0.978206</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.838534</v>
+        <v>0.975288</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.72695</v>
+        <v>0.7280799999999999</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.11648</v>
+        <v>0.091687</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.634373</v>
+        <v>0.8895</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.260073</v>
+        <v>0.294926</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.329398</v>
+        <v>0.26349</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.9605320000000001</v>
+        <v>0.999653</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11823,10 +11823,10 @@
         <v>0</v>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G265" t="n">
-        <v>0.303457</v>
+        <v>0.5665559999999999</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.176155</v>
+        <v>0.094056</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.715879</v>
+        <v>0.96221</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.916049</v>
+        <v>0.994047</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.378905</v>
+        <v>0.276812</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.138451</v>
+        <v>0.1185</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.09243999999999999</v>
+        <v>0.082051</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.431655</v>
+        <v>0.362025</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0.288027</v>
+        <v>0.285602</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>0.354889</v>
+        <v>0.336986</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.139625</v>
+        <v>0.219967</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.599135</v>
+        <v>0.610907</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12339,10 +12339,10 @@
         <v>9e-06</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
-        <v>0.376298</v>
+        <v>0.731957</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>0.6445380000000001</v>
+        <v>0.522973</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.219812</v>
+        <v>0.146887</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.150814</v>
+        <v>0.073159</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.320871</v>
+        <v>0.290258</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.273384</v>
+        <v>0.107581</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.238957</v>
+        <v>0.100103</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.240384</v>
+        <v>0.143271</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.256677</v>
+        <v>0.182916</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12726,10 +12726,10 @@
         <v>0.005459</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G286" t="n">
-        <v>0.308126</v>
+        <v>0.54736</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12769,10 +12769,10 @@
         <v>2.6e-05</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.340679</v>
+        <v>0.9555670000000001</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12812,10 +12812,10 @@
         <v>0.002963</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0.434037</v>
+        <v>0.661056</v>
       </c>
       <c r="H288" t="n">
         <v>1</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.179194</v>
+        <v>0.126399</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.259859</v>
+        <v>0.241504</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12941,10 +12941,10 @@
         <v>0.012553</v>
       </c>
       <c r="F291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0.319232</v>
+        <v>0.581604</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.244493</v>
+        <v>0.127708</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13027,10 +13027,10 @@
         <v>0.000597</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0.432602</v>
+        <v>0.56621</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.226984</v>
+        <v>0.061646</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.190719</v>
+        <v>0.125043</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.999201</v>
+        <v>1</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.454509</v>
+        <v>0.442921</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.240764</v>
+        <v>0.199016</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0.527399</v>
+        <v>0.645351</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0.675444</v>
+        <v>0.8259339999999999</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.230169</v>
+        <v>0.1289</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.292348</v>
+        <v>0.170068</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.97622</v>
+        <v>0.998689</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.97929</v>
+        <v>0.999746</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.21869</v>
+        <v>0.204877</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.470339</v>
+        <v>0.362486</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.422096</v>
+        <v>0.250718</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0.511678</v>
+        <v>0.640456</v>
       </c>
       <c r="H308" t="n">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.852888</v>
+        <v>0.982171</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.186842</v>
+        <v>0.168243</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.313812</v>
+        <v>0.272296</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.16824</v>
+        <v>0.032667</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.293912</v>
+        <v>0.152861</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
